--- a/survey_templates/034_love_survey--survey_templates.xlsx
+++ b/survey_templates/034_love_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>First Name 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Last Name 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Age 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Income 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Favorite Food</t>
+          <t>Favorite Food 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very positive'}</t>
+          <t>Very positive</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very_negative'}</t>
+          <t>very_negative</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very Negative'}</t>
+          <t>Very Negative</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'tinder'}</t>
+          <t>tinder</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Tinder'}</t>
+          <t>Tinder</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bumble'}</t>
+          <t>bumble</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bumble'}</t>
+          <t>Bumble</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'okcupid'}</t>
+          <t>okcupid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'OkCupid'}</t>
+          <t>OkCupid</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'plenty_of_fish'}</t>
+          <t>plenty_of_fish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Plenty of Fish'}</t>
+          <t>Plenty of Fish</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'match.com'}</t>
+          <t>match.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Match.com'}</t>
+          <t>Match.com</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'yellow'}</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Yellow'}</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cat'}</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cat'}</t>
+          <t>Cat</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dog'}</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dog'}</t>
+          <t>Dog</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_10'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 10'}</t>
+          <t>Less than 10</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'$10-$50'}</t>
+          <t>$10-$50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '$10-$50'}</t>
+          <t>$10-$50</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'$50-$100'}</t>
+          <t>$50-$100</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '$50-$100'}</t>
+          <t>$50-$100</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'more_than_$100'}</t>
+          <t>more_than_$100</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'More than $100'}</t>
+          <t>More than $100</t>
         </is>
       </c>
     </row>
